--- a/phase5_1/input/mpn_map.xlsx
+++ b/phase5_1/input/mpn_map.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="21">
   <si>
     <t>Item ID</t>
   </si>
@@ -57,22 +57,31 @@
     <t>DEMO-003</t>
   </si>
   <si>
-    <t>863-1523-2-ND</t>
-  </si>
-  <si>
     <t>erp</t>
   </si>
   <si>
     <t>DEMO-004</t>
   </si>
   <si>
-    <t>1649-SHT40-AD1B-R3TR-ND</t>
-  </si>
-  <si>
-    <t>non_catalog</t>
-  </si>
-  <si>
     <t>custom part</t>
+  </si>
+  <si>
+    <t>BC2385-ND</t>
+  </si>
+  <si>
+    <t>3667-SILD867170-ND</t>
+  </si>
+  <si>
+    <t>584-LT1076HVIR#PBF</t>
+  </si>
+  <si>
+    <t>457-REX22DTA116E</t>
+  </si>
+  <si>
+    <t>571-10219128-02</t>
+  </si>
+  <si>
+    <t>225-DCM30V10L20S1PFB</t>
   </si>
 </sst>
 </file>
@@ -879,8 +888,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5703125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -929,30 +943,75 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" t="s">
         <v>14</v>
       </c>
-      <c r="B5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" t="s">
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>17</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>